--- a/lorenzo-playwright-kdf/excelFramework/testcases/WA/LSTP_WA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/WA/LSTP_WA_WF001.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk32\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\WA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\WA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD376C9D-AF1A-496E-AD13-C95EE3A26798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488C99C1-D0F8-4BFF-865E-3A2C59130AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E44575C4-E91D-4AE7-BBDA-60192DD75907}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{E44575C4-E91D-4AE7-BBDA-60192DD75907}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -1779,7 +1779,7 @@
         <v>157</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>

--- a/lorenzo-playwright-kdf/excelFramework/testcases/WA/LSTP_WA_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/WA/LSTP_WA_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\WA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488C99C1-D0F8-4BFF-865E-3A2C59130AC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BE6CA1A-A17C-45CB-ADC9-6DDD30BBDBC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{E44575C4-E91D-4AE7-BBDA-60192DD75907}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{E44575C4-E91D-4AE7-BBDA-60192DD75907}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="327">
   <si>
     <t>StepNo</t>
   </si>
@@ -1030,6 +1030,9 @@
   </si>
   <si>
     <t>Confirm logout</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2272,7 +2275,7 @@
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
@@ -2345,7 +2348,7 @@
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3" t="s">
-        <v>19</v>
+        <v>326</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
